--- a/customers.xlsx
+++ b/customers.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rohit\opencv_projects\RME QUOTE GENERATOR\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rohit\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A56DCAC-A6A4-49F4-A478-094899A22125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4957584A-245E-478A-9133-C590EA745A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20544" yWindow="0" windowWidth="20832" windowHeight="16656" xr2:uid="{8FB97326-46DA-481B-B445-56520A7F1BED}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
   <si>
     <t>Contact Name</t>
   </si>
@@ -89,16 +89,22 @@
     <t>Integration Specialist</t>
   </si>
   <si>
-    <t>Port Hedland, WA, 6722</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maintenance Coordinator      </t>
   </si>
   <si>
-    <t>Port Hedland, WA, 6723</t>
-  </si>
-  <si>
     <t>Murray Cooper</t>
+  </si>
+  <si>
+    <t>James  Girgis</t>
+  </si>
+  <si>
+    <t>Project Engineer - Rail</t>
+  </si>
+  <si>
+    <t>Fortescue - Hedland Operations - Rail, Port Hedland</t>
+  </si>
+  <si>
+    <t>Port Hedland, WA, 6721</t>
   </si>
 </sst>
 </file>
@@ -487,11 +493,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B63B4DD-A4CC-45C1-BB13-D0639F9CE57F}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="13.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.109375" customWidth="1"/>
-    <col min="3" max="3" width="39.109375" customWidth="1"/>
+    <col min="3" max="3" width="43.44140625" customWidth="1"/>
     <col min="4" max="4" width="30.21875" customWidth="1"/>
     <col min="5" max="5" width="28.44140625" customWidth="1"/>
     <col min="6" max="6" width="22.21875" customWidth="1"/>
@@ -562,15 +568,15 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
@@ -579,7 +585,24 @@
         <v>13</v>
       </c>
       <c r="E5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
